--- a/sources/prototype_step5b.xlsx
+++ b/sources/prototype_step5b.xlsx
@@ -722,6 +722,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
@@ -779,6 +784,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
@@ -831,6 +841,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
@@ -881,6 +896,11 @@
       <c r="O9" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>c4222188-365d-401c-a75a-8d64d256a8cc</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -5602,6 +5622,11 @@
       <c r="K99" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>4e36f2e9-e904-45da-b205-e22a2d153bbd</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">

--- a/sources/prototype_step5b.xlsx
+++ b/sources/prototype_step5b.xlsx
@@ -2680,7 +2680,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2866,7 +2866,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3912,7 +3912,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4036,7 +4036,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4651,6 +4651,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -4768,6 +4773,11 @@
       <c r="A81" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
